--- a/설계도 및 기타 자료/설계 통합.xlsx
+++ b/설계도 및 기타 자료/설계 통합.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kalec\Documents\GitHub\Security_Coding\vscode_workspace\SweetScoopDEV\설계도 및 기타 자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3A07DC-07D2-464E-BEDB-9A5A70EB783F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BCAF31-5E0C-4751-A129-88FFF0C9EEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="915" windowWidth="21765" windowHeight="11865" activeTab="2" xr2:uid="{252A36F0-B911-437C-AAE0-3BFD0A28F79C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{252A36F0-B911-437C-AAE0-3BFD0A28F79C}"/>
   </bookViews>
   <sheets>
     <sheet name="usecase" sheetId="2" r:id="rId1"/>
@@ -40,30 +40,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="183">
   <si>
     <t>1. 고객 및 주문/결제 도메인 (Customer &amp; Order)</t>
   </si>
@@ -3255,368 +3233,6045 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>-- ==========================================</t>
-  </si>
-  <si>
-    <t>-- 1. 마스터 테이블 (독립적인 최상위 엔티티)</t>
-  </si>
-  <si>
-    <t>CREATE TABLE CUSTOMER (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    customer_id INT NOT NULL AUTO_INCREMENT COMMENT '고객 고유 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    phone_number VARCHAR(20) COMMENT '연락처',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (customer_id)</t>
-  </si>
-  <si>
-    <t>) COMMENT '비회원/고객 일반';</t>
-  </si>
-  <si>
-    <t>CREATE TABLE BRANCH (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    branch_id INT NOT NULL AUTO_INCREMENT COMMENT '지점 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    branch_name VARCHAR(50) NOT NULL COMMENT '지점명',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    location VARCHAR(100) COMMENT '위치/주소',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (branch_id)</t>
-  </si>
-  <si>
-    <t>) COMMENT '지점 정보';</t>
-  </si>
-  <si>
-    <t>CREATE TABLE MENU (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    menu_id INT NOT NULL AUTO_INCREMENT COMMENT '메뉴 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    menu_name VARCHAR(50) NOT NULL COMMENT '메뉴명',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    price INT NOT NULL COMMENT '가격',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    sale_status VARCHAR(20) COMMENT '판매 상태 (품절여부 등)',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (menu_id)</t>
-  </si>
-  <si>
-    <t>) COMMENT '메뉴';</t>
-  </si>
-  <si>
-    <t>CREATE TABLE ITEM (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    item_id INT NOT NULL AUTO_INCREMENT COMMENT '물품 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    item_name VARCHAR(50) NOT NULL COMMENT '물품명',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (item_id)</t>
-  </si>
-  <si>
-    <t>) COMMENT '재고 물품 (본사/지점 공통)';</t>
-  </si>
-  <si>
-    <t>CREATE TABLE PROMOTION (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    event_id INT NOT NULL AUTO_INCREMENT COMMENT '이벤트 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    event_name VARCHAR(100) NOT NULL COMMENT '이벤트명',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    start_date DATE COMMENT '시작일',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    end_date DATE COMMENT '종료일',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (event_id)</t>
-  </si>
-  <si>
-    <t>) COMMENT '이벤트/홍보';</t>
-  </si>
-  <si>
-    <t>CREATE TABLE HQ_MANAGER (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    admin_id VARCHAR(50) NOT NULL COMMENT '관리자 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    password VARCHAR(255) NOT NULL COMMENT '비밀번호',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (admin_id)</t>
-  </si>
-  <si>
-    <t>) COMMENT '본사 관리자';</t>
-  </si>
-  <si>
-    <t>-- 2. 1차 종속 테이블 (마스터를 1개 참조)</t>
-  </si>
-  <si>
-    <t>CREATE TABLE MEMBER (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    member_id INT NOT NULL AUTO_INCREMENT COMMENT '회원 고유 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    customer_id INT NOT NULL COMMENT '고객 ID (외래키)',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    order_count INT DEFAULT 0 COMMENT '누적 주문 횟수',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (member_id),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    FOREIGN KEY (customer_id) REFERENCES CUSTOMER(customer_id) ON DELETE CASCADE</t>
-  </si>
-  <si>
-    <t>) COMMENT '회원';</t>
-  </si>
-  <si>
-    <t>CREATE TABLE BRANCH_MANAGER (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    manager_id VARCHAR(50) NOT NULL COMMENT '점주 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    branch_id INT NOT NULL COMMENT '담당 지점 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (manager_id),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    FOREIGN KEY (branch_id) REFERENCES BRANCH(branch_id)</t>
-  </si>
-  <si>
-    <t>) COMMENT '지점 관리자/점주';</t>
-  </si>
-  <si>
-    <t>CREATE TABLE KIOSK (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    kiosk_id INT NOT NULL AUTO_INCREMENT COMMENT '기기 고유 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    branch_id INT NOT NULL COMMENT '소속 지점 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    status VARCHAR(20) COMMENT '기기 상태 (정상, 고장 등)',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (kiosk_id),</t>
-  </si>
-  <si>
-    <t>) COMMENT '개별 키오스크 기기';</t>
-  </si>
-  <si>
-    <t>CREATE TABLE SALES (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    sales_id INT NOT NULL AUTO_INCREMENT COMMENT '매출 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    branch_id INT NOT NULL COMMENT '지점 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    sales_date DATE NOT NULL COMMENT '매출 일자',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    total_amount INT DEFAULT 0 COMMENT '총액',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (sales_id),</t>
-  </si>
-  <si>
-    <t>) COMMENT '매출 상세';</t>
-  </si>
-  <si>
-    <t>-- 3. 핵심 트랜잭션 및 다대다 연결 테이블</t>
-  </si>
-  <si>
-    <t>CREATE TABLE COUPON (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    coupon_id INT NOT NULL AUTO_INCREMENT COMMENT '쿠폰 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    member_id INT NOT NULL COMMENT '회원 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    issue_date DATE COMMENT '발급일',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    expiry_date DATE COMMENT '만료일',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (coupon_id),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    FOREIGN KEY (member_id) REFERENCES MEMBER(member_id)</t>
-  </si>
-  <si>
-    <t>) COMMENT '쿠폰';</t>
-  </si>
-  <si>
-    <t>CREATE TABLE ORDERS (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    order_id INT NOT NULL AUTO_INCREMENT COMMENT '주문 번호',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    customer_id INT NOT NULL COMMENT '고객 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    order_type VARCHAR(20) COMMENT '주문 유형 (매장/포장 등)',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    language VARCHAR(20) COMMENT '언어 설정',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    status VARCHAR(20) COMMENT '주문 상태',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (order_id),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    FOREIGN KEY (customer_id) REFERENCES CUSTOMER(customer_id),</t>
-  </si>
-  <si>
-    <t>) COMMENT '주문';</t>
-  </si>
-  <si>
-    <t>CREATE TABLE ORDER_ITEM (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    order_item_id INT NOT NULL AUTO_INCREMENT COMMENT '상세 항목 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    order_id INT NOT NULL COMMENT '주문 번호',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    menu_id INT NOT NULL COMMENT '메뉴 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    flavor VARCHAR(30) COMMENT '맛 옵션',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    container VARCHAR(30) COMMENT '용기 옵션',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    insulation_option VARCHAR(30) COMMENT '보온/보냉 옵션',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    quantity INT DEFAULT 1 COMMENT '수량',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (order_item_id),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    FOREIGN KEY (order_id) REFERENCES ORDERS(order_id) ON DELETE CASCADE,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    FOREIGN KEY (menu_id) REFERENCES MENU(menu_id)</t>
-  </si>
-  <si>
-    <t>) COMMENT '주문 상세 항목';</t>
-  </si>
-  <si>
-    <t>CREATE TABLE PAYMENT (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    payment_id INT NOT NULL AUTO_INCREMENT COMMENT '결제 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    member_id INT COMMENT '회원 ID (비회원결제가능)',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    method VARCHAR(20) NOT NULL COMMENT '결제 수단',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    amount INT NOT NULL COMMENT '결제 금액',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    point_used INT DEFAULT 0 COMMENT '사용 포인트',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    point_earned INT DEFAULT 0 COMMENT '적립 포인트',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (payment_id),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    FOREIGN KEY (order_id) REFERENCES ORDERS(order_id),</t>
-  </si>
-  <si>
-    <t>) COMMENT '결제';</t>
-  </si>
-  <si>
-    <t>CREATE TABLE BRANCH_INVENTORY (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    item_id INT NOT NULL COMMENT '물품 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    stock_level INT DEFAULT 0 COMMENT '현재 재고량',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (item_id, branch_id),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    FOREIGN KEY (item_id) REFERENCES ITEM(item_id),</t>
-  </si>
-  <si>
-    <t>) COMMENT '지점 재고';</t>
-  </si>
-  <si>
-    <t>CREATE TABLE HQ_INVENTORY (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    request_id INT NOT NULL AUTO_INCREMENT COMMENT '발주 요청 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    branch_id INT NOT NULL COMMENT '요청 지점 ID',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    approval_status VARCHAR(20) COMMENT '승인 상태',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    delivery_status VARCHAR(20) COMMENT '배송 상태',</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PRIMARY KEY (request_id),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    FOREIGN KEY (branch_id) REFERENCES BRANCH(branch_id),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    FOREIGN KEY (item_id) REFERENCES ITEM(item_id)</t>
-  </si>
-  <si>
-    <t>) COMMENT '본사 물류/재고 (발주이력)';</t>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>BRANCH</t>
+    </r>
+  </si>
+  <si>
+    <t>(</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  branch_id   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AUTO_INCREMENT COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'지점 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  branch_name </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'지점명'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'위치/주소'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (branch_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'지점 정보'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>BRANCH_INVENTORY</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  item_id     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'물품 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  branch_id   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'지점 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  stock_level </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'현재 재고량'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (item_id, branch_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'지점 재고'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>BRANCH_MANAGER</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  manager_id </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'점주 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  branch_id  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'담당 지점 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (manager_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'지점 관리자/점주'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>COUPON</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  coupon_id   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AUTO_INCREMENT COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'쿠폰 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  member_id   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'회원 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  issue_date  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'발급일'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>expiry_date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'만료일'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (coupon_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'쿠폰'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>CS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  cs_id      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'문의 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  title      STRING      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'문의 제목'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  content    STRING      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'문의 내용'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'문의일자'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (cs_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'문의게시판 테이블'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>CUSTOMER</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  customer_id  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AUTO_INCREMENT COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'고객 고유 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  phone_number </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'연락처'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (customer_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'비회원/고객 일반'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>HQ_INVENTORY</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  request_id      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AUTO_INCREMENT COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'발주 요청 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  branch_id       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'요청 지점 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  item_id         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'물품 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  approval_status </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'승인 상태'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  delivery_status </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'배송 상태'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (request_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'본사 물류/재고 (발주이력)'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>HQ_MANAGER</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  마스터를      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">    ,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  cs_id </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'문의 ID'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'본사 관리자'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>ITEM</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  item_id   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AUTO_INCREMENT COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'물품 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  item_name </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'물품명'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (item_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'재고 물품 (본사/지점 공통)'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>KIOSK</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  kiosk_id  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AUTO_INCREMENT COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'기기 고유 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  branch_id </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'소속 지점 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'기기 상태 (정상, 고장 등)'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (kiosk_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'개별 키오스크 기기'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>MEMBER</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  member_id    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AUTO_INCREMENT COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'회원 고유 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  customer_id  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'고객 ID (외래키)'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  order_count  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'누적 주문 횟수'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">    ,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (member_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'회원'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>MENU</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  menu_id     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AUTO_INCREMENT COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'메뉴 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  menu_name   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'메뉴명'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  price       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'가격'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  sale_status </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'판매 상태 (품절여부 등)'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (menu_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'메뉴'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>ORDER_ITEM</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  order_item_id     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AUTO_INCREMENT COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'상세 항목 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  order_id          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'주문 번호'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  menu_id           </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'메뉴 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  flavor            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'맛 옵션'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  container         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'용기 옵션'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  insulation_option </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'보온/보냉 옵션'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  quantity          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'수량'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">    ,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (order_item_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'주문 상세 항목'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>ORDERS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  order_id    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AUTO_INCREMENT COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'주문 번호'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  customer_id </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'고객 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  branch_id   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'지점 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  order_type  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'주문 유형 (매장/포장 등)'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>language</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'언어 설정'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'주문 상태'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (order_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'주문'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PAYMENT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  payment_id   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AUTO_INCREMENT COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'결제 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  order_id     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'주문 번호'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  member_id    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'회원 ID (비회원결제가능)'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  method       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'결제 수단'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  amount       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'결제 금액'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  point_used   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'사용 포인트'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  point_earned </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'적립 포인트'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (payment_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'결제'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PROMOTION</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  event_id   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AUTO_INCREMENT COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'이벤트 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  event_name </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'이벤트명'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>start_date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'시작일'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  end_date   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'종료일'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (event_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'이벤트/홍보'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6F42C1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>SALES</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  sales_id     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AUTO_INCREMENT COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'매출 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  branch_id    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'지점 ID'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  sales_date   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'매출 일자'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  total_amount </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF005CC5"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'총액'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (sales_id)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">) COMMENT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>'매출 상세'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ALTER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> MEMBER</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>ADD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD73A49"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> FK_CUSTOMER_TO_MEMBER</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3672,6 +9327,36 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFD73A49"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF24292E"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF6F42C1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF032F62"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF005CC5"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3716,7 +9401,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3736,6 +9421,12 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3816,76 +9507,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>14289</xdr:rowOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>107155</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>337705</xdr:colOff>
-      <xdr:row>111</xdr:row>
-      <xdr:rowOff>204789</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>157673</xdr:colOff>
+      <xdr:row>208</xdr:row>
+      <xdr:rowOff>186688</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
+        <xdr:cNvPr id="2" name="그림 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CB9F25E-55CF-7BEC-4FF0-F28E55B31441}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="17806989"/>
-          <a:ext cx="12453505" cy="6267450"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>157</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>332048</xdr:colOff>
-      <xdr:row>192</xdr:row>
-      <xdr:rowOff>199083</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3503E491-67D0-BDF8-3DAB-F63D4335DD78}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78D621AA-4A25-3B44-0E8C-BAD9CAE90EAA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3901,8 +9537,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="32899350"/>
-          <a:ext cx="10619048" cy="7533333"/>
+          <a:off x="0" y="33325593"/>
+          <a:ext cx="15052393" cy="11438095"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4232,7 +9868,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43551332-AF15-4873-8D9B-1B498F5C432A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4243,17 +9879,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{202A5DA6-4E49-4508-BC8E-6F1D8D58AC40}">
   <dimension ref="A1:A82"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="1" width="159" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="38.25">
+    <row r="1" spans="1:1" ht="34.9">
       <c r="A1" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="21.75">
+    <row r="2" spans="1:1" ht="19.5">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -4366,7 +10002,7 @@
     <row r="26" spans="1:1">
       <c r="A26" s="6"/>
     </row>
-    <row r="27" spans="1:1" ht="21.75">
+    <row r="27" spans="1:1" ht="19.5">
       <c r="A27" s="3" t="s">
         <v>17</v>
       </c>
@@ -4461,7 +10097,7 @@
     <row r="47" spans="1:1">
       <c r="A47" s="6"/>
     </row>
-    <row r="48" spans="1:1" ht="21.75">
+    <row r="48" spans="1:1" ht="19.5">
       <c r="A48" s="3" t="s">
         <v>33</v>
       </c>
@@ -4502,7 +10138,7 @@
     <row r="56" spans="1:1">
       <c r="A56" s="6"/>
     </row>
-    <row r="57" spans="1:1" ht="21.75">
+    <row r="57" spans="1:1" ht="19.5">
       <c r="A57" s="3" t="s">
         <v>39</v>
       </c>
@@ -4579,7 +10215,7 @@
     <row r="73" spans="1:1">
       <c r="A73" s="6"/>
     </row>
-    <row r="74" spans="1:1" ht="21.75">
+    <row r="74" spans="1:1" ht="19.5">
       <c r="A74" s="3" t="s">
         <v>52</v>
       </c>
@@ -4623,689 +10259,705 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45399EE8-9D3D-48C6-8C47-CDD1B53EFF2F}">
   <dimension ref="A1:A155"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <cols>
+    <col min="1" max="1" width="68.5625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="s">
+      <c r="A1" s="7" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" t="s">
+      <c r="A2" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>63</v>
+      <c r="A3" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>65</v>
+      <c r="A5" s="8" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>66</v>
+      <c r="A6" s="8" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>68</v>
+      <c r="A7" s="8" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>69</v>
+      <c r="A9" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>70</v>
+      <c r="A11" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>71</v>
+      <c r="A12" s="8" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>72</v>
+      <c r="A13" s="8" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>73</v>
+      <c r="A14" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
+      <c r="A15" s="8" t="s">
         <v>75</v>
       </c>
     </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
     <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>76</v>
+      <c r="A18" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" t="s">
+      <c r="A19" s="8" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" t="s">
+      <c r="A20" s="8" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" t="s">
+      <c r="A21" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" t="s">
+      <c r="A22" s="8" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
+    <row r="24" spans="1:1">
+      <c r="A24" s="7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
+    <row r="27" spans="1:1">
+      <c r="A27" s="8" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
+    <row r="28" spans="1:1">
+      <c r="A28" s="8" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
+    <row r="29" spans="1:1">
+      <c r="A29" s="8" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
+    <row r="30" spans="1:1">
+      <c r="A30" s="8" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
+    <row r="31" spans="1:1">
+      <c r="A31" s="8" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
+    <row r="33" spans="1:1">
+      <c r="A33" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
+    <row r="34" spans="1:1">
+      <c r="A34" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="8" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
+    <row r="36" spans="1:1">
+      <c r="A36" s="8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
+    <row r="37" spans="1:1">
+      <c r="A37" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
+    <row r="38" spans="1:1">
+      <c r="A38" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
+    <row r="39" spans="1:1">
+      <c r="A39" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
+    <row r="41" spans="1:1">
+      <c r="A41" s="8" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
+    <row r="43" spans="1:1">
+      <c r="A43" s="7" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
+    <row r="44" spans="1:1">
+      <c r="A44" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="8" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
+    <row r="46" spans="1:1">
+      <c r="A46" s="8" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
+    <row r="47" spans="1:1">
+      <c r="A47" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" s="8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
+    <row r="50" spans="1:1">
+      <c r="A50" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>63</v>
-      </c>
-    </row>
     <row r="51" spans="1:1">
-      <c r="A51" t="s">
+      <c r="A51" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="8" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
+    <row r="53" spans="1:1">
+      <c r="A53" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
+    <row r="54" spans="1:1">
+      <c r="A54" s="8" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>67</v>
-      </c>
-    </row>
     <row r="55" spans="1:1">
-      <c r="A55" t="s">
+      <c r="A55" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" t="s">
+      <c r="A56" s="8" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" t="s">
+      <c r="A57" s="8" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" t="s">
+      <c r="A58" s="8" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" t="s">
+      <c r="A60" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" t="s">
+      <c r="A61" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="8" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
+    <row r="63" spans="1:1">
+      <c r="A63" s="8" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
+    <row r="64" spans="1:1">
+      <c r="A64" s="8" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
+    <row r="66" spans="1:1">
+      <c r="A66" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
+    <row r="67" spans="1:1">
+      <c r="A67" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
+    <row r="69" spans="1:1">
+      <c r="A69" s="8" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
+    <row r="70" spans="1:1">
+      <c r="A70" s="8" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
+    <row r="71" spans="1:1">
+      <c r="A71" s="8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
+    <row r="73" spans="1:1">
+      <c r="A73" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
+    <row r="74" spans="1:1">
+      <c r="A74" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
+    <row r="76" spans="1:1">
+      <c r="A76" s="8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
+    <row r="77" spans="1:1">
+      <c r="A77" s="8" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
+    <row r="78" spans="1:1">
+      <c r="A78" s="8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
+    <row r="79" spans="1:1">
+      <c r="A79" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
+    <row r="81" spans="1:1">
+      <c r="A81" s="7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
+    <row r="82" spans="1:1">
+      <c r="A82" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
+    <row r="84" spans="1:1">
+      <c r="A84" s="8" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
+    <row r="85" spans="1:1">
+      <c r="A85" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="8" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" t="s">
+    <row r="87" spans="1:1">
+      <c r="A87" s="8" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
-      <c r="A87" t="s">
-        <v>63</v>
+    <row r="88" spans="1:1">
+      <c r="A88" s="8" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
+      <c r="A89" s="8" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" t="s">
+      <c r="A91" s="7" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" t="s">
+      <c r="A92" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
-      <c r="A93" t="s">
+    <row r="94" spans="1:1">
+      <c r="A94" s="8" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
+    <row r="95" spans="1:1">
+      <c r="A95" s="8" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
-      <c r="A95" t="s">
+    <row r="96" spans="1:1">
+      <c r="A96" s="8" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
-      <c r="A96" t="s">
+    <row r="97" spans="1:1">
+      <c r="A97" s="8" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" t="e" cm="1">
-        <f t="array" ref="A98">-- 🔴 시스템의 정중앙 핵심 테이블</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" t="s">
+      <c r="A98" s="8" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" t="s">
+      <c r="A100" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" t="s">
+      <c r="A101" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="8" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>122</v>
-      </c>
-    </row>
     <row r="103" spans="1:1">
-      <c r="A103" t="s">
+      <c r="A103" s="8" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" t="s">
+      <c r="A104" s="8" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" t="s">
+      <c r="A105" s="8" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" t="s">
+      <c r="A106" s="8" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" t="s">
+      <c r="A107" s="8" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" t="s">
-        <v>112</v>
+      <c r="A108" s="8" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" t="s">
-        <v>144</v>
+      <c r="A109" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="8" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" t="s">
-        <v>146</v>
+      <c r="A111" s="8" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" t="s">
-        <v>147</v>
+      <c r="A113" s="7" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" t="s">
-        <v>148</v>
+      <c r="A114" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" t="s">
+      <c r="A115" s="8" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" t="s">
+      <c r="A116" s="8" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" t="s">
+      <c r="A117" s="8" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" t="s">
+      <c r="A118" s="8" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" t="s">
+      <c r="A119" s="8" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" t="s">
+      <c r="A120" s="8" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" t="s">
+      <c r="A121" s="8" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" t="s">
+      <c r="A122" s="8" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" t="s">
+      <c r="A124" s="7" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" t="s">
+      <c r="A125" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="8" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
-      <c r="A126" t="s">
-        <v>147</v>
-      </c>
-    </row>
     <row r="127" spans="1:1">
-      <c r="A127" t="s">
+      <c r="A127" s="8" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" t="s">
+      <c r="A128" s="8" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" t="s">
+      <c r="A129" s="8" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" t="s">
+      <c r="A130" s="8" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" t="s">
+      <c r="A131" s="8" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" t="s">
+      <c r="A132" s="8" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" t="s">
+      <c r="A133" s="8" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" t="s">
+      <c r="A134" s="8" t="s">
         <v>166</v>
       </c>
     </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
     <row r="137" spans="1:1">
-      <c r="A137" t="s">
-        <v>167</v>
+      <c r="A137" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" t="s">
+      <c r="A138" s="8" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" t="s">
-        <v>122</v>
+      <c r="A139" s="8" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" t="s">
-        <v>169</v>
+      <c r="A140" s="8" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" t="s">
-        <v>170</v>
+      <c r="A141" s="8" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" t="s">
-        <v>171</v>
+      <c r="A142" s="8" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" t="s">
-        <v>172</v>
+      <c r="A143" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="7" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" t="s">
-        <v>173</v>
+      <c r="A146" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" t="s">
-        <v>174</v>
+      <c r="A147" s="8" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" t="s">
-        <v>175</v>
+      <c r="A148" s="8" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" t="s">
-        <v>168</v>
+      <c r="A149" s="8" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" t="s">
-        <v>176</v>
+      <c r="A150" s="8" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" t="s">
-        <v>177</v>
+      <c r="A151" s="8" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" t="s">
-        <v>179</v>
+      <c r="A152" s="8" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="154" spans="1:1">
-      <c r="A154" t="s">
-        <v>180</v>
+      <c r="A154" s="7" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="155" spans="1:1">
-      <c r="A155" t="s">
-        <v>181</v>
+      <c r="A155" s="8" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/설계도 및 기타 자료/설계 통합.xlsx
+++ b/설계도 및 기타 자료/설계 통합.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kalec\Documents\GitHub\Security_Coding\vscode_workspace\SweetScoopDEV\설계도 및 기타 자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06D8DB3-0C9E-4DCB-8BDC-F14E5CEE28F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55352033-0B11-4F70-81F8-25C7B20DFF46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{252A36F0-B911-437C-AAE0-3BFD0A28F79C}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="374">
   <si>
     <t>(</t>
   </si>
@@ -4728,6 +4728,10 @@
   </si>
   <si>
     <t>+checkStatus()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CREATE DATABASE sweetscoop default CHARACTER SET UTF8; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4873,18 +4877,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4899,6 +4891,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5413,7 +5417,7 @@
   <dimension ref="A1:E86"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.4375" style="15" customWidth="1"/>
+    <col min="1" max="1" width="10.4375" style="11" customWidth="1"/>
     <col min="2" max="2" width="20.5625" style="3" customWidth="1"/>
     <col min="3" max="3" width="51.375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.9375" style="3" customWidth="1"/>
@@ -5439,946 +5443,986 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="12" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10" t="s">
+      <c r="A3" s="15"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="E3" s="11"/>
+      <c r="E3" s="12"/>
     </row>
     <row r="4" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="10" t="s">
+      <c r="A4" s="15"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="E4" s="11"/>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="10" t="s">
+      <c r="A5" s="15"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="E5" s="11"/>
+      <c r="E5" s="12"/>
     </row>
     <row r="6" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8" t="s">
+      <c r="A6" s="15"/>
+      <c r="B6" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="10" t="s">
+      <c r="A7" s="15"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="E7" s="11"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="8" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="8" t="s">
+      <c r="A8" s="15"/>
+      <c r="B8" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="7" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="10" t="s">
+      <c r="A9" s="15"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="7" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="10" t="s">
+      <c r="A11" s="15"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="E11" s="12"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="10" t="s">
+      <c r="A12" s="15"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="E12" s="12"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="10" t="s">
+      <c r="A13" s="15"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="E13" s="12"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="8" t="s">
+      <c r="A14" s="15"/>
+      <c r="B14" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="7" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="10" t="s">
+      <c r="A15" s="15"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="7" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10" t="s">
+      <c r="A16" s="15"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="E16" s="12"/>
+      <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="10" t="s">
+      <c r="A17" s="15"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="E17" s="12"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="10" t="s">
+      <c r="A18" s="15"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="E18" s="12"/>
+      <c r="E18" s="8"/>
     </row>
     <row r="19" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="10" t="s">
+      <c r="A19" s="15"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="E19" s="12"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="20" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="10" t="s">
+      <c r="A20" s="15"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="E20" s="12"/>
+      <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="7" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="10" t="s">
+      <c r="A22" s="15"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="7" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="10" t="s">
+      <c r="A23" s="15"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="7" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="10" t="s">
+      <c r="A24" s="15"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="E24" s="12"/>
+      <c r="E24" s="8"/>
     </row>
     <row r="25" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="10" t="s">
+      <c r="A25" s="15"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="E25" s="12"/>
+      <c r="E25" s="8"/>
     </row>
     <row r="26" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10" t="s">
+      <c r="A26" s="15"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="E26" s="12"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A27" s="7"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10" t="s">
+      <c r="A27" s="15"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="E27" s="12"/>
+      <c r="E27" s="8"/>
     </row>
     <row r="28" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A28" s="7"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="10" t="s">
+      <c r="A28" s="15"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="E28" s="12"/>
+      <c r="E28" s="8"/>
     </row>
     <row r="29" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A29" s="7"/>
-      <c r="B29" s="8" t="s">
+      <c r="A29" s="15"/>
+      <c r="B29" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="12" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A30" s="7"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="10" t="s">
+      <c r="A30" s="15"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="E30" s="11"/>
+      <c r="E30" s="12"/>
     </row>
     <row r="31" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A31" s="7"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="10" t="s">
+      <c r="A31" s="15"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="12"/>
     </row>
     <row r="32" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A32" s="7"/>
-      <c r="B32" s="8" t="s">
+      <c r="A32" s="15"/>
+      <c r="B32" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="7" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A33" s="7"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="10" t="s">
+      <c r="A33" s="15"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="7" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A34" s="7"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="10" t="s">
+      <c r="A34" s="15"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="7" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A35" s="7"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="10" t="s">
+      <c r="A35" s="15"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="E35" s="12"/>
+      <c r="E35" s="8"/>
     </row>
     <row r="36" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A36" s="7"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="10" t="s">
+      <c r="A36" s="15"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="E36" s="12"/>
+      <c r="E36" s="8"/>
     </row>
     <row r="37" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A37" s="7"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="10" t="s">
+      <c r="A37" s="15"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="E37" s="12"/>
+      <c r="E37" s="8"/>
     </row>
     <row r="38" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A38" s="7"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="10" t="s">
+      <c r="A38" s="15"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="E38" s="12"/>
+      <c r="E38" s="8"/>
     </row>
     <row r="39" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A39" s="7"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="10" t="s">
+      <c r="A39" s="15"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E39" s="12"/>
+      <c r="E39" s="8"/>
     </row>
     <row r="40" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A40" s="7"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="10" t="s">
+      <c r="A40" s="15"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="E40" s="12"/>
+      <c r="E40" s="8"/>
     </row>
     <row r="41" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A41" s="7"/>
-      <c r="B41" s="8" t="s">
+      <c r="A41" s="15"/>
+      <c r="B41" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="7" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A42" s="7"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="10" t="s">
+      <c r="A42" s="15"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="7" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A43" s="7"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="10" t="s">
+      <c r="A43" s="15"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="7" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A44" s="7"/>
-      <c r="B44" s="13" t="s">
+      <c r="A44" s="15"/>
+      <c r="B44" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="7" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A45" s="7"/>
-      <c r="B45" s="13" t="s">
+      <c r="A45" s="15"/>
+      <c r="B45" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="7" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="7" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A47" s="7"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="10" t="s">
+      <c r="A47" s="15"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="7" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A48" s="7"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="10" t="s">
+      <c r="A48" s="15"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="E48" s="12"/>
+      <c r="E48" s="8"/>
     </row>
     <row r="49" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A49" s="7"/>
-      <c r="B49" s="8" t="s">
+      <c r="A49" s="15"/>
+      <c r="B49" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="D49" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="7" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A50" s="7"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="10" t="s">
+      <c r="A50" s="15"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="E50" s="7" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A51" s="7"/>
-      <c r="B51" s="8" t="s">
+      <c r="A51" s="15"/>
+      <c r="B51" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C51" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="7" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A52" s="7"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="12"/>
+      <c r="A52" s="15"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="8"/>
     </row>
     <row r="53" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A53" s="7"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="10" t="s">
+      <c r="A53" s="15"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="7" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A54" s="7"/>
-      <c r="B54" s="8" t="s">
+      <c r="A54" s="15"/>
+      <c r="B54" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="C54" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E54" s="12" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A55" s="7"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="10" t="s">
+      <c r="A55" s="15"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="E55" s="11"/>
+      <c r="E55" s="12"/>
     </row>
     <row r="56" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A56" s="7"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="10" t="s">
+      <c r="A56" s="15"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="E56" s="11"/>
+      <c r="E56" s="12"/>
     </row>
     <row r="57" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A57" s="7"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="10" t="s">
+      <c r="A57" s="15"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="E57" s="11"/>
+      <c r="E57" s="12"/>
     </row>
     <row r="58" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A58" s="7"/>
-      <c r="B58" s="8" t="s">
+      <c r="A58" s="15"/>
+      <c r="B58" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="D58" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E58" s="7" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A59" s="7"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="10" t="s">
+      <c r="A59" s="15"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E59" s="7" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A60" s="7"/>
-      <c r="B60" s="8" t="s">
+      <c r="A60" s="15"/>
+      <c r="B60" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D60" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E60" s="7" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A61" s="7"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="10" t="s">
+      <c r="A61" s="15"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E61" s="7" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="D62" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="E62" s="7" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A63" s="7"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="10" t="s">
+      <c r="A63" s="15"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="E63" s="10" t="s">
+      <c r="E63" s="7" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A64" s="7"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="10" t="s">
+      <c r="A64" s="15"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E64" s="12"/>
+      <c r="E64" s="8"/>
     </row>
     <row r="65" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A65" s="7"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="10" t="s">
+      <c r="A65" s="15"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="E65" s="12"/>
+      <c r="E65" s="8"/>
     </row>
     <row r="66" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="C66" s="9" t="s">
+      <c r="C66" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="D66" s="10" t="s">
+      <c r="D66" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E66" s="11" t="s">
+      <c r="E66" s="12" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A67" s="7"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="10" t="s">
+      <c r="A67" s="15"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="E67" s="11"/>
+      <c r="E67" s="12"/>
     </row>
     <row r="68" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A68" s="7"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="10" t="s">
+      <c r="A68" s="15"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="E68" s="11"/>
+      <c r="E68" s="12"/>
     </row>
     <row r="69" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A69" s="7"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="10" t="s">
+      <c r="A69" s="15"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="E69" s="11"/>
+      <c r="E69" s="12"/>
     </row>
     <row r="70" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A70" s="7"/>
-      <c r="B70" s="8"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="10" t="s">
+      <c r="A70" s="15"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="E70" s="11"/>
+      <c r="E70" s="12"/>
     </row>
     <row r="71" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A71" s="7"/>
-      <c r="B71" s="8" t="s">
+      <c r="A71" s="15"/>
+      <c r="B71" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="D71" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E71" s="12" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A72" s="7"/>
-      <c r="B72" s="8"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="10" t="s">
+      <c r="A72" s="15"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="E72" s="11"/>
+      <c r="E72" s="12"/>
     </row>
     <row r="73" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A73" s="7"/>
-      <c r="B73" s="8"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="10" t="s">
+      <c r="A73" s="15"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="E73" s="11"/>
+      <c r="E73" s="12"/>
     </row>
     <row r="74" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A74" s="7"/>
-      <c r="B74" s="8" t="s">
+      <c r="A74" s="15"/>
+      <c r="B74" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="C74" s="14" t="s">
         <v>356</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D74" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="12" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A75" s="7"/>
-      <c r="B75" s="8"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="10" t="s">
+      <c r="A75" s="15"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="E75" s="11"/>
+      <c r="E75" s="12"/>
     </row>
     <row r="76" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A76" s="7"/>
-      <c r="B76" s="8" t="s">
+      <c r="A76" s="15"/>
+      <c r="B76" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D76" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="E76" s="7" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A77" s="7"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="10" t="s">
+      <c r="A77" s="15"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="14"/>
+      <c r="D77" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="E77" s="7" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A78" s="7"/>
-      <c r="B78" s="8"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="10" t="s">
+      <c r="A78" s="15"/>
+      <c r="B78" s="13"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="E78" s="12"/>
+      <c r="E78" s="8"/>
     </row>
     <row r="79" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A79" s="7"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="10" t="s">
+      <c r="A79" s="15"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="E79" s="12"/>
+      <c r="E79" s="8"/>
     </row>
     <row r="80" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A80" s="7"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="10" t="s">
+      <c r="A80" s="15"/>
+      <c r="B80" s="13"/>
+      <c r="C80" s="14"/>
+      <c r="D80" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="E80" s="12"/>
+      <c r="E80" s="8"/>
     </row>
     <row r="81" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A81" s="7"/>
-      <c r="B81" s="8" t="s">
+      <c r="A81" s="15"/>
+      <c r="B81" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="C81" s="9" t="s">
+      <c r="C81" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="D81" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E81" s="11" t="s">
+      <c r="E81" s="12" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A82" s="7"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="10" t="s">
+      <c r="A82" s="15"/>
+      <c r="B82" s="13"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="E82" s="11"/>
+      <c r="E82" s="12"/>
     </row>
     <row r="83" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A83" s="7"/>
-      <c r="B83" s="8"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="10" t="s">
+      <c r="A83" s="15"/>
+      <c r="B83" s="13"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="E83" s="11"/>
+      <c r="E83" s="12"/>
     </row>
     <row r="84" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A84" s="7"/>
-      <c r="B84" s="8"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="10" t="s">
+      <c r="A84" s="15"/>
+      <c r="B84" s="13"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="E84" s="11"/>
+      <c r="E84" s="12"/>
     </row>
     <row r="85" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A85" s="7"/>
-      <c r="B85" s="8" t="s">
+      <c r="A85" s="15"/>
+      <c r="B85" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="C85" s="9" t="s">
+      <c r="C85" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="D85" s="10" t="s">
+      <c r="D85" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E85" s="7" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="16.899999999999999" customHeight="1">
-      <c r="A86" s="7"/>
-      <c r="B86" s="8"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="10" t="s">
+      <c r="A86" s="15"/>
+      <c r="B86" s="13"/>
+      <c r="C86" s="14"/>
+      <c r="D86" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="E86" s="10" t="s">
+      <c r="E86" s="7" t="s">
         <v>372</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="B21:B28"/>
+    <mergeCell ref="C21:C28"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="B8:B13"/>
+    <mergeCell ref="C8:C13"/>
+    <mergeCell ref="B14:B20"/>
+    <mergeCell ref="C14:C20"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="B32:B40"/>
+    <mergeCell ref="C32:C40"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="E54:E57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="B66:B70"/>
+    <mergeCell ref="C66:C70"/>
     <mergeCell ref="E81:E84"/>
     <mergeCell ref="B85:B86"/>
     <mergeCell ref="C85:C86"/>
@@ -6395,46 +6439,6 @@
     <mergeCell ref="C71:C73"/>
     <mergeCell ref="E71:E73"/>
     <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="B66:B70"/>
-    <mergeCell ref="C66:C70"/>
-    <mergeCell ref="E54:E57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="C54:C57"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="B32:B40"/>
-    <mergeCell ref="C32:C40"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="B21:B28"/>
-    <mergeCell ref="C21:C28"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="B8:B13"/>
-    <mergeCell ref="C8:C13"/>
-    <mergeCell ref="B14:B20"/>
-    <mergeCell ref="C14:C20"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6451,7 +6455,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
